--- a/output_data/charts/0500000US39117.xlsx
+++ b/output_data/charts/0500000US39117.xlsx
@@ -167,10 +167,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -212,16 +212,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$15</c:f>
+              <c:f>Sheet1!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.2586950273066974</c:v>
                 </c:pt>
@@ -253,16 +256,19 @@
                   <c:v>0.3706637994454191</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.4373927958833619</c:v>
+                  <c:v>0.4344967555669897</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.4345973583297827</c:v>
+                  <c:v>0.431683280792934</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.4669458908761603</c:v>
+                  <c:v>0.4671971005464791</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.4551201011378002</c:v>
+                  <c:v>0.4608942472529016</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.4759651515573246</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -292,10 +298,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -337,16 +343,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$15</c:f>
+              <c:f>Sheet1!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.3592986490370796</c:v>
                 </c:pt>
@@ -378,16 +387,19 @@
                   <c:v>0.687567200497991</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.740423098913665</c:v>
+                  <c:v>0.7346425406626076</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.7555744922596223</c:v>
+                  <c:v>0.7497656982193065</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.8829522300203759</c:v>
+                  <c:v>0.8777642495115666</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.8990026689141734</c:v>
+                  <c:v>0.8852541944186831</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.8962618643360146</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -417,10 +429,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -462,16 +474,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$15</c:f>
+              <c:f>Sheet1!$D$2:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.098016671457315</c:v>
                 </c:pt>
@@ -503,16 +518,19 @@
                   <c:v>1.595834983871881</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.695254431103488</c:v>
+                  <c:v>1.69225052168196</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.786678028689106</c:v>
+                  <c:v>1.783533554855017</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.930043015621463</c:v>
+                  <c:v>1.931081348925447</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.017137238376177</c:v>
+                  <c:v>2.043110474102802</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.201686753694993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -542,10 +560,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -587,16 +605,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$15</c:f>
+              <c:f>Sheet1!$E$2:$E$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.1379706812302386</c:v>
                 </c:pt>
@@ -628,16 +649,19 @@
                   <c:v>0.2037236149623677</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2029731275014294</c:v>
+                  <c:v>0.2029557213503702</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2101974151398949</c:v>
+                  <c:v>0.2101615972281389</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2292279827937514</c:v>
+                  <c:v>0.2293513039046352</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.2191319005478298</c:v>
+                  <c:v>0.2220161312986539</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.2171069112366744</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -667,10 +691,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -712,16 +736,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$15</c:f>
+              <c:f>Sheet1!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.195745903995401</c:v>
                 </c:pt>
@@ -753,16 +780,19 @@
                   <c:v>1.474166713824911</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.42652944539737</c:v>
+                  <c:v>1.429265643312466</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.505467973299247</c:v>
+                  <c:v>1.508051461191105</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.57063617840163</c:v>
+                  <c:v>1.585638644278959</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.668773704171934</c:v>
+                  <c:v>1.686198465559396</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.725721602137668</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -792,10 +822,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -837,16 +867,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$15</c:f>
+              <c:f>Sheet1!$G$2:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>96.95027306697327</c:v>
                 </c:pt>
@@ -878,16 +911,19 @@
                   <c:v>95.66804368739743</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>95.49742710120069</c:v>
+                  <c:v>95.5063888174256</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>95.30748473228235</c:v>
+                  <c:v>95.31680440771349</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>94.92019470228662</c:v>
+                  <c:v>94.90896735283292</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>94.74083438685209</c:v>
+                  <c:v>94.70252648736756</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>94.48325771703733</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1006,13 +1042,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1428750</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1320,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" style="1" customWidth="1"/>
@@ -1590,22 +1626,22 @@
         <v>2020</v>
       </c>
       <c r="B12" s="2">
-        <v>0.4373927958833619</v>
+        <v>0.4344967555669897</v>
       </c>
       <c r="C12" s="2">
-        <v>0.740423098913665</v>
+        <v>0.7346425406626076</v>
       </c>
       <c r="D12" s="2">
-        <v>1.695254431103488</v>
+        <v>1.69225052168196</v>
       </c>
       <c r="E12" s="2">
-        <v>0.2029731275014294</v>
+        <v>0.2029557213503702</v>
       </c>
       <c r="F12" s="2">
-        <v>1.42652944539737</v>
+        <v>1.429265643312466</v>
       </c>
       <c r="G12" s="2">
-        <v>95.49742710120069</v>
+        <v>95.5063888174256</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1613,22 +1649,22 @@
         <v>2021</v>
       </c>
       <c r="B13" s="2">
-        <v>0.4345973583297827</v>
+        <v>0.431683280792934</v>
       </c>
       <c r="C13" s="2">
-        <v>0.7555744922596223</v>
+        <v>0.7497656982193065</v>
       </c>
       <c r="D13" s="2">
-        <v>1.786678028689106</v>
+        <v>1.783533554855017</v>
       </c>
       <c r="E13" s="2">
-        <v>0.2101974151398949</v>
+        <v>0.2101615972281389</v>
       </c>
       <c r="F13" s="2">
-        <v>1.505467973299247</v>
+        <v>1.508051461191105</v>
       </c>
       <c r="G13" s="2">
-        <v>95.30748473228235</v>
+        <v>95.31680440771349</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1636,22 +1672,22 @@
         <v>2022</v>
       </c>
       <c r="B14" s="2">
-        <v>0.4669458908761603</v>
+        <v>0.4671971005464791</v>
       </c>
       <c r="C14" s="2">
-        <v>0.8829522300203759</v>
+        <v>0.8777642495115666</v>
       </c>
       <c r="D14" s="2">
-        <v>1.930043015621463</v>
+        <v>1.931081348925447</v>
       </c>
       <c r="E14" s="2">
-        <v>0.2292279827937514</v>
+        <v>0.2293513039046352</v>
       </c>
       <c r="F14" s="2">
-        <v>1.57063617840163</v>
+        <v>1.585638644278959</v>
       </c>
       <c r="G14" s="2">
-        <v>94.92019470228662</v>
+        <v>94.90896735283292</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1659,22 +1695,45 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2">
-        <v>0.4551201011378002</v>
+        <v>0.4608942472529016</v>
       </c>
       <c r="C15" s="2">
-        <v>0.8990026689141734</v>
+        <v>0.8852541944186831</v>
       </c>
       <c r="D15" s="2">
-        <v>2.017137238376177</v>
+        <v>2.043110474102802</v>
       </c>
       <c r="E15" s="2">
-        <v>0.2191319005478298</v>
+        <v>0.2220161312986539</v>
       </c>
       <c r="F15" s="2">
-        <v>1.668773704171934</v>
+        <v>1.686198465559396</v>
       </c>
       <c r="G15" s="2">
-        <v>94.74083438685209</v>
+        <v>94.70252648736756</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.4759651515573246</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.8962618643360146</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2.201686753694993</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.2171069112366744</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1.725721602137668</v>
+      </c>
+      <c r="G16" s="2">
+        <v>94.48325771703733</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39117.xlsx
+++ b/output_data/charts/0500000US39117.xlsx
@@ -229,31 +229,31 @@
                   <c:v>0.2586950273066974</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2613966047166288</c:v>
+                  <c:v>0.2614191324332089</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3013863773357444</c:v>
+                  <c:v>0.301429637710283</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3529310493242662</c:v>
+                  <c:v>0.3529816908683924</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3720557511233222</c:v>
+                  <c:v>0.3720983484557919</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3518910568175316</c:v>
+                  <c:v>0.3520018315542455</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3177966101694916</c:v>
+                  <c:v>0.3178512112708322</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3435639028859368</c:v>
+                  <c:v>0.3437312021998797</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3529445250903709</c:v>
+                  <c:v>0.3559935066784382</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3706637994454191</c:v>
+                  <c:v>0.3708106884057971</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.4344967555669897</c:v>
@@ -360,31 +360,31 @@
                   <c:v>0.3592986490370796</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.4308735242581794</c:v>
+                  <c:v>0.4337833955759839</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.4649961250322914</c:v>
+                  <c:v>0.4679336280645346</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.5050070299274052</c:v>
+                  <c:v>0.50794926246915</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.5237400188889842</c:v>
+                  <c:v>0.5266622778143515</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.5836241917949305</c:v>
+                  <c:v>0.5866697192570758</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.5497022446174988</c:v>
+                  <c:v>0.5583872630433538</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.6298671552908841</c:v>
+                  <c:v>0.6387671507547764</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.6461161870605983</c:v>
+                  <c:v>0.6578760003417538</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.687567200497991</c:v>
+                  <c:v>0.6963315217391304</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.7346425406626076</c:v>
@@ -488,34 +488,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.098016671457315</c:v>
+                  <c:v>1.095142282265019</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.20070088759946</c:v>
+                  <c:v>1.192186153404194</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.328970406728092</c:v>
+                  <c:v>1.317678130562095</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.411724197297065</c:v>
+                  <c:v>1.394708144406819</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.396640050370625</c:v>
+                  <c:v>1.382488479262673</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.470504091091148</c:v>
+                  <c:v>1.453796182354119</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.408612001832341</c:v>
+                  <c:v>1.397399919821316</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.460146587265231</c:v>
+                  <c:v>1.426484489129501</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.579711382460934</c:v>
+                  <c:v>1.549283741064563</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.595834983871881</c:v>
+                  <c:v>1.573822463768116</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1.69225052168196</c:v>
@@ -622,31 +622,31 @@
                   <c:v>0.1379706812302386</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.146496998247781</c:v>
+                  <c:v>0.1465096236713588</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.1521283618932805</c:v>
+                  <c:v>0.1521501980823333</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1520759806031391</c:v>
+                  <c:v>0.1520978017562991</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1659941043473284</c:v>
+                  <c:v>0.1660131093110456</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1773759798592436</c:v>
+                  <c:v>0.1774318175314083</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1889601465872652</c:v>
+                  <c:v>0.1889926121069813</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1889601465872652</c:v>
+                  <c:v>0.1919165878949328</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1907038966214101</c:v>
+                  <c:v>0.1993563637399254</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2037236149623677</c:v>
+                  <c:v>0.2122961956521739</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.2029557213503702</c:v>
@@ -753,31 +753,31 @@
                   <c:v>1.195745903995401</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.278258121965932</c:v>
+                  <c:v>1.272622809537489</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.343322138982175</c:v>
+                  <c:v>1.329161164379629</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.288341797939801</c:v>
+                  <c:v>1.277047580784021</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.287885292349961</c:v>
+                  <c:v>1.276583564702178</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.350346169251016</c:v>
+                  <c:v>1.330738631485562</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.420064131928539</c:v>
+                  <c:v>1.383082297691999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.379981676591846</c:v>
+                  <c:v>1.337687261894532</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.36339054450232</c:v>
+                  <c:v>1.327143792897218</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.474166713824911</c:v>
+                  <c:v>1.446444746376812</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1.429265643312466</c:v>
@@ -881,34 +881,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>96.95027306697327</c:v>
+                  <c:v>96.95314745616557</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>96.68227386321202</c:v>
+                  <c:v>96.69347888537777</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>96.40919659002842</c:v>
+                  <c:v>96.43164724120112</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>96.28991994490832</c:v>
+                  <c:v>96.31521551971531</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>96.25368478291978</c:v>
+                  <c:v>96.27615422045396</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>96.06625851118613</c:v>
+                  <c:v>96.09936181781758</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>96.11486486486487</c:v>
+                  <c:v>96.15428669606551</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>95.99748053137883</c:v>
+                  <c:v>96.06141330812638</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>95.86713346426437</c:v>
+                  <c:v>95.9103465952781</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>95.66804368739743</c:v>
+                  <c:v>95.70029438405797</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>95.5063888174256</c:v>
@@ -1402,7 +1402,7 @@
         <v>0.3592986490370796</v>
       </c>
       <c r="D2" s="2">
-        <v>1.098016671457315</v>
+        <v>1.095142282265019</v>
       </c>
       <c r="E2" s="2">
         <v>0.1379706812302386</v>
@@ -1411,7 +1411,7 @@
         <v>1.195745903995401</v>
       </c>
       <c r="G2" s="2">
-        <v>96.95027306697327</v>
+        <v>96.95314745616557</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1419,22 +1419,22 @@
         <v>2011</v>
       </c>
       <c r="B3" s="2">
-        <v>0.2613966047166288</v>
+        <v>0.2614191324332089</v>
       </c>
       <c r="C3" s="2">
-        <v>0.4308735242581794</v>
+        <v>0.4337833955759839</v>
       </c>
       <c r="D3" s="2">
-        <v>1.20070088759946</v>
+        <v>1.192186153404194</v>
       </c>
       <c r="E3" s="2">
-        <v>0.146496998247781</v>
+        <v>0.1465096236713588</v>
       </c>
       <c r="F3" s="2">
-        <v>1.278258121965932</v>
+        <v>1.272622809537489</v>
       </c>
       <c r="G3" s="2">
-        <v>96.68227386321202</v>
+        <v>96.69347888537777</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1442,22 +1442,22 @@
         <v>2012</v>
       </c>
       <c r="B4" s="2">
-        <v>0.3013863773357444</v>
+        <v>0.301429637710283</v>
       </c>
       <c r="C4" s="2">
-        <v>0.4649961250322914</v>
+        <v>0.4679336280645346</v>
       </c>
       <c r="D4" s="2">
-        <v>1.328970406728092</v>
+        <v>1.317678130562095</v>
       </c>
       <c r="E4" s="2">
-        <v>0.1521283618932805</v>
+        <v>0.1521501980823333</v>
       </c>
       <c r="F4" s="2">
-        <v>1.343322138982175</v>
+        <v>1.329161164379629</v>
       </c>
       <c r="G4" s="2">
-        <v>96.40919659002842</v>
+        <v>96.43164724120112</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1465,22 +1465,22 @@
         <v>2013</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3529310493242662</v>
+        <v>0.3529816908683924</v>
       </c>
       <c r="C5" s="2">
-        <v>0.5050070299274052</v>
+        <v>0.50794926246915</v>
       </c>
       <c r="D5" s="2">
-        <v>1.411724197297065</v>
+        <v>1.394708144406819</v>
       </c>
       <c r="E5" s="2">
-        <v>0.1520759806031391</v>
+        <v>0.1520978017562991</v>
       </c>
       <c r="F5" s="2">
-        <v>1.288341797939801</v>
+        <v>1.277047580784021</v>
       </c>
       <c r="G5" s="2">
-        <v>96.28991994490832</v>
+        <v>96.31521551971531</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1488,22 +1488,22 @@
         <v>2014</v>
       </c>
       <c r="B6" s="2">
-        <v>0.3720557511233222</v>
+        <v>0.3720983484557919</v>
       </c>
       <c r="C6" s="2">
-        <v>0.5237400188889842</v>
+        <v>0.5266622778143515</v>
       </c>
       <c r="D6" s="2">
-        <v>1.396640050370625</v>
+        <v>1.382488479262673</v>
       </c>
       <c r="E6" s="2">
-        <v>0.1659941043473284</v>
+        <v>0.1660131093110456</v>
       </c>
       <c r="F6" s="2">
-        <v>1.287885292349961</v>
+        <v>1.276583564702178</v>
       </c>
       <c r="G6" s="2">
-        <v>96.25368478291978</v>
+        <v>96.27615422045396</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1511,22 +1511,22 @@
         <v>2015</v>
       </c>
       <c r="B7" s="2">
-        <v>0.3518910568175316</v>
+        <v>0.3520018315542455</v>
       </c>
       <c r="C7" s="2">
-        <v>0.5836241917949305</v>
+        <v>0.5866697192570758</v>
       </c>
       <c r="D7" s="2">
-        <v>1.470504091091148</v>
+        <v>1.453796182354119</v>
       </c>
       <c r="E7" s="2">
-        <v>0.1773759798592436</v>
+        <v>0.1774318175314083</v>
       </c>
       <c r="F7" s="2">
-        <v>1.350346169251016</v>
+        <v>1.330738631485562</v>
       </c>
       <c r="G7" s="2">
-        <v>96.06625851118613</v>
+        <v>96.09936181781758</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1534,22 +1534,22 @@
         <v>2016</v>
       </c>
       <c r="B8" s="2">
-        <v>0.3177966101694916</v>
+        <v>0.3178512112708322</v>
       </c>
       <c r="C8" s="2">
-        <v>0.5497022446174988</v>
+        <v>0.5583872630433538</v>
       </c>
       <c r="D8" s="2">
-        <v>1.408612001832341</v>
+        <v>1.397399919821316</v>
       </c>
       <c r="E8" s="2">
-        <v>0.1889601465872652</v>
+        <v>0.1889926121069813</v>
       </c>
       <c r="F8" s="2">
-        <v>1.420064131928539</v>
+        <v>1.383082297691999</v>
       </c>
       <c r="G8" s="2">
-        <v>96.11486486486487</v>
+        <v>96.15428669606551</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1557,22 +1557,22 @@
         <v>2017</v>
       </c>
       <c r="B9" s="2">
-        <v>0.3435639028859368</v>
+        <v>0.3437312021998797</v>
       </c>
       <c r="C9" s="2">
-        <v>0.6298671552908841</v>
+        <v>0.6387671507547764</v>
       </c>
       <c r="D9" s="2">
-        <v>1.460146587265231</v>
+        <v>1.426484489129501</v>
       </c>
       <c r="E9" s="2">
-        <v>0.1889601465872652</v>
+        <v>0.1919165878949328</v>
       </c>
       <c r="F9" s="2">
-        <v>1.379981676591846</v>
+        <v>1.337687261894532</v>
       </c>
       <c r="G9" s="2">
-        <v>95.99748053137883</v>
+        <v>96.06141330812638</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1580,22 +1580,22 @@
         <v>2018</v>
       </c>
       <c r="B10" s="2">
-        <v>0.3529445250903709</v>
+        <v>0.3559935066784382</v>
       </c>
       <c r="C10" s="2">
-        <v>0.6461161870605983</v>
+        <v>0.6578760003417538</v>
       </c>
       <c r="D10" s="2">
-        <v>1.579711382460934</v>
+        <v>1.549283741064563</v>
       </c>
       <c r="E10" s="2">
-        <v>0.1907038966214101</v>
+        <v>0.1993563637399254</v>
       </c>
       <c r="F10" s="2">
-        <v>1.36339054450232</v>
+        <v>1.327143792897218</v>
       </c>
       <c r="G10" s="2">
-        <v>95.86713346426437</v>
+        <v>95.9103465952781</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1603,22 +1603,22 @@
         <v>2019</v>
       </c>
       <c r="B11" s="2">
-        <v>0.3706637994454191</v>
+        <v>0.3708106884057971</v>
       </c>
       <c r="C11" s="2">
-        <v>0.687567200497991</v>
+        <v>0.6963315217391304</v>
       </c>
       <c r="D11" s="2">
-        <v>1.595834983871881</v>
+        <v>1.573822463768116</v>
       </c>
       <c r="E11" s="2">
-        <v>0.2037236149623677</v>
+        <v>0.2122961956521739</v>
       </c>
       <c r="F11" s="2">
-        <v>1.474166713824911</v>
+        <v>1.446444746376812</v>
       </c>
       <c r="G11" s="2">
-        <v>95.66804368739743</v>
+        <v>95.70029438405797</v>
       </c>
     </row>
     <row r="12" spans="1:7">
